--- a/05. Res/modelos/coeficientes_quasipoisson.xlsx
+++ b/05. Res/modelos/coeficientes_quasipoisson.xlsx
@@ -466,16 +466,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.54517452368271</v>
+        <v>-1.75767420440689</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0709372860947038</v>
+        <v>0.073676859681839</v>
       </c>
       <c r="D2" t="n">
-        <v>-21.7822616109086</v>
+        <v>-23.85652987922</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000666433022788187</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000226365375649101</v>
       </c>
     </row>
     <row r="3">
@@ -483,16 +483,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="n">
-        <v>0.667123434716253</v>
+        <v>0.853744031750938</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0458142481290385</v>
+        <v>0.0450528552338197</v>
       </c>
       <c r="D3" t="n">
-        <v>14.5614838605942</v>
+        <v>18.9498318657074</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0000000000000000000000000000000000000000000000056473071453244</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000650234761680017</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +500,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>0.569306441492496</v>
+        <v>0.758061857671197</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0429784005571561</v>
+        <v>0.0421104059557753</v>
       </c>
       <c r="D4" t="n">
-        <v>13.2463384889204</v>
+        <v>18.001770357363</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000000000000000000000000000000000000000519514897630356</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000257990567252775</v>
       </c>
     </row>
     <row r="5">
@@ -517,16 +517,16 @@
         <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>-4.13444862220598</v>
+        <v>-3.96296614019794</v>
       </c>
       <c r="C5" t="n">
-        <v>1.18717811280241</v>
+        <v>1.19376490439427</v>
       </c>
       <c r="D5" t="n">
-        <v>-3.4825849446014</v>
+        <v>-3.31972076378707</v>
       </c>
       <c r="E5" t="n">
-        <v>0.000496849119020301</v>
+        <v>0.000901457591258419</v>
       </c>
     </row>
     <row r="6">
@@ -534,16 +534,16 @@
         <v>9</v>
       </c>
       <c r="B6" t="n">
-        <v>0.046071604076446</v>
+        <v>0.0271981818607928</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0145311752365019</v>
+        <v>0.0145574807799749</v>
       </c>
       <c r="D6" t="n">
-        <v>3.17053530265849</v>
+        <v>1.86833026070049</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00152212762841991</v>
+        <v>0.0617195200798246</v>
       </c>
     </row>
     <row r="7">
@@ -551,16 +551,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.205115787045603</v>
+        <v>0.0803617976539967</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0528199734582382</v>
+        <v>0.0551952276907174</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.88329969926579</v>
+        <v>1.45595554210408</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000103126944147672</v>
+        <v>0.145408637132406</v>
       </c>
     </row>
     <row r="8">
@@ -568,16 +568,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.293659861096734</v>
+        <v>-0.0118967947846802</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0543667558300195</v>
+        <v>0.0562374939671735</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.40146007635396</v>
+        <v>-0.211545606773028</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0000000662789624844216</v>
+        <v>0.832462060101974</v>
       </c>
     </row>
     <row r="9">
@@ -585,16 +585,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.155502145485465</v>
+        <v>0.0435368790390522</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0561667148145566</v>
+        <v>0.0582201997714738</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.76858181930134</v>
+        <v>0.747796799219915</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00563131376189519</v>
+        <v>0.454584820749906</v>
       </c>
     </row>
     <row r="10">
@@ -602,16 +602,16 @@
         <v>13</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.289365582283758</v>
+        <v>-0.0935349312020425</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0576934695157053</v>
+        <v>0.0598342608760883</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.01556908802281</v>
+        <v>-1.56323366968208</v>
       </c>
       <c r="E10" t="n">
-        <v>0.000000529837880638848</v>
+        <v>0.118001400182197</v>
       </c>
     </row>
     <row r="11">
@@ -619,16 +619,16 @@
         <v>14</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.436430387660355</v>
+        <v>-0.17367063233217</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0612675629755006</v>
+        <v>0.0630416567285677</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.12335151693356</v>
+        <v>-2.7548551441141</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00000000000106172259495732</v>
+        <v>0.00587307296770148</v>
       </c>
     </row>
     <row r="12">
@@ -636,16 +636,16 @@
         <v>15</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.414597592865965</v>
+        <v>-0.766375773543299</v>
       </c>
       <c r="C12" t="n">
-        <v>0.071826156259083</v>
+        <v>0.0747936649986503</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.77223694625223</v>
+        <v>-10.246533226539</v>
       </c>
       <c r="E12" t="n">
-        <v>0.00000000784991646014314</v>
+        <v>0.0000000000000000000000012681924187951</v>
       </c>
     </row>
     <row r="13">
@@ -653,16 +653,16 @@
         <v>16</v>
       </c>
       <c r="B13" t="n">
-        <v>0.034325202286913</v>
+        <v>-0.128234999239622</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0665945958918031</v>
+        <v>0.0682087797684186</v>
       </c>
       <c r="D13" t="n">
-        <v>0.515435251573289</v>
+        <v>-1.88003655357864</v>
       </c>
       <c r="E13" t="n">
-        <v>0.606250255639978</v>
+        <v>0.0601065445604528</v>
       </c>
     </row>
     <row r="14">
@@ -670,16 +670,16 @@
         <v>17</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.195132606414289</v>
+        <v>-0.317410775439775</v>
       </c>
       <c r="C14" t="n">
-        <v>0.066817662456131</v>
+        <v>0.0681008995116296</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.92037463211772</v>
+        <v>-4.66088961696564</v>
       </c>
       <c r="E14" t="n">
-        <v>0.00349703405939505</v>
+        <v>0.00000315326768872162</v>
       </c>
     </row>
     <row r="15">
@@ -687,16 +687,16 @@
         <v>18</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.236770446639478</v>
+        <v>-0.299127714732782</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0685763950447517</v>
+        <v>0.0696300331601899</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.45265227903809</v>
+        <v>-4.29595824038476</v>
       </c>
       <c r="E15" t="n">
-        <v>0.000555376264882104</v>
+        <v>0.0000174134945020019</v>
       </c>
     </row>
     <row r="16">
@@ -704,16 +704,16 @@
         <v>19</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.0867297596137126</v>
+        <v>-0.130211269249286</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0198849171728102</v>
+        <v>0.0199563936864052</v>
       </c>
       <c r="D16" t="n">
-        <v>-4.36158515823758</v>
+        <v>-6.52478956345651</v>
       </c>
       <c r="E16" t="n">
-        <v>0.000012927643554512</v>
+        <v>0.0000000000684813910202773</v>
       </c>
     </row>
     <row r="17">
@@ -721,16 +721,16 @@
         <v>20</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.167277569646248</v>
+        <v>-0.108722711381466</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0212864400345819</v>
+        <v>0.021693809114982</v>
       </c>
       <c r="D17" t="n">
-        <v>-7.85840983154017</v>
+        <v>-5.01169300445171</v>
       </c>
       <c r="E17" t="n">
-        <v>0.00000000000000393605434185732</v>
+        <v>0.00000054062268411573</v>
       </c>
     </row>
     <row r="18">
@@ -738,16 +738,16 @@
         <v>21</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.153284040671566</v>
+        <v>-0.148079488131958</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0400443036139067</v>
+        <v>0.0409985215072108</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.82786131454496</v>
+        <v>-3.61182507778758</v>
       </c>
       <c r="E18" t="n">
-        <v>0.000129354845312566</v>
+        <v>0.000304226242183846</v>
       </c>
     </row>
     <row r="19">
@@ -755,16 +755,16 @@
         <v>22</v>
       </c>
       <c r="B19" t="n">
-        <v>0.147132102102957</v>
+        <v>0.0799800884829761</v>
       </c>
       <c r="C19" t="n">
-        <v>0.023224728997373</v>
+        <v>0.022810876626872</v>
       </c>
       <c r="D19" t="n">
-        <v>6.33514828610484</v>
+        <v>3.50622598996292</v>
       </c>
       <c r="E19" t="n">
-        <v>0.000000000238303976535481</v>
+        <v>0.00045474543004992</v>
       </c>
     </row>
     <row r="20">
@@ -772,16 +772,16 @@
         <v>23</v>
       </c>
       <c r="B20" t="n">
-        <v>0.274487353057273</v>
+        <v>0.171498622285334</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0248481663157252</v>
+        <v>0.024814872835827</v>
       </c>
       <c r="D20" t="n">
-        <v>11.0465838633559</v>
+        <v>6.91112235069484</v>
       </c>
       <c r="E20" t="n">
-        <v>0.000000000000000000000000000238156282525449</v>
+        <v>0.00000000000484235763637132</v>
       </c>
     </row>
     <row r="21">
@@ -789,16 +789,16 @@
         <v>24</v>
       </c>
       <c r="B21" t="n">
-        <v>0.310545132764254</v>
+        <v>0.164389369040611</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0261670354587479</v>
+        <v>0.0264386431852347</v>
       </c>
       <c r="D21" t="n">
-        <v>11.8677995928819</v>
+        <v>6.21776873680183</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0000000000000000000000000000000184665147253395</v>
+        <v>0.000000000506630364100233</v>
       </c>
     </row>
     <row r="22">
@@ -806,16 +806,16 @@
         <v>25</v>
       </c>
       <c r="B22" t="n">
-        <v>0.0917326753013945</v>
+        <v>0.0428628624921881</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0138352930911091</v>
+        <v>0.0140317445297412</v>
       </c>
       <c r="D22" t="n">
-        <v>6.63033841764755</v>
+        <v>3.0547065905695</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0000000000336929026786822</v>
+        <v>0.00225351157761173</v>
       </c>
     </row>
     <row r="23">
@@ -823,16 +823,16 @@
         <v>26</v>
       </c>
       <c r="B23" t="n">
-        <v>0.000218242899085799</v>
+        <v>0.000295258212902932</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0000456869711064443</v>
+        <v>0.0000459804871105258</v>
       </c>
       <c r="D23" t="n">
-        <v>4.77691765946409</v>
+        <v>6.42138070858632</v>
       </c>
       <c r="E23" t="n">
-        <v>0.000001783013264998</v>
+        <v>0.000000000135759691720585</v>
       </c>
     </row>
     <row r="24">
@@ -840,13 +840,13 @@
         <v>27</v>
       </c>
       <c r="B24" t="n">
-        <v>0.121758440968355</v>
+        <v>0.113170422984952</v>
       </c>
       <c r="C24" t="n">
-        <v>0.000879230587251868</v>
+        <v>0.000812480286845817</v>
       </c>
       <c r="D24" t="n">
-        <v>138.4829448995</v>
+        <v>139.290053946168</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -857,13 +857,13 @@
         <v>28</v>
       </c>
       <c r="B25" t="n">
-        <v>0.265464198244439</v>
+        <v>0.276409031029294</v>
       </c>
       <c r="C25" t="n">
-        <v>0.00198706537111321</v>
+        <v>0.00207805267933408</v>
       </c>
       <c r="D25" t="n">
-        <v>133.596107155608</v>
+        <v>133.013486028598</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -874,13 +874,13 @@
         <v>29</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.0712138961627018</v>
+        <v>-0.0702240349502626</v>
       </c>
       <c r="C26" t="n">
-        <v>0.00150276723891918</v>
+        <v>0.00154235350198856</v>
       </c>
       <c r="D26" t="n">
-        <v>-47.3885072274536</v>
+        <v>-45.5304408877229</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
